--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -377,37 +377,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CM-20260820-00000153</t>
+          <t>CM-20260826-00000134</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INC-20260820-00004356</t>
+          <t>INC-20260826-00004799</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-20 11:49:22</t>
+          <t>2026-08-26 13:55:14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-20 12:00:01</t>
+          <t/>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1970-01-01 00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12793-ETH_LINK_DOWN</t>
+          <t>2507160001-ETH_LOS_CAIDA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -417,27 +417,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>Total</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0131149</t>
+          <t>01348334</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0131149_LM_Nuevo_Caqueta</t>
+          <t>01348334_LM_MC_Rokys_Angamos</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>01:42:00</t>
+          <t>02:38:05</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -462,22 +462,22 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>RIMAC</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-20 11:51:13</t>
+          <t>2026-08-26 14:01:36</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-20 11:57:50</t>
+          <t/>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -554,37 +554,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CM-20260820-00000152</t>
+          <t>CM-20260826-00000080</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INC-20260820-00004356</t>
+          <t>INC-20260826-00002852</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-20 11:49:22</t>
+          <t>2026-08-26 10:41:04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-20 12:00:01</t>
+          <t/>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1970-01-01 00:00:00</t>
+          <t/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12793-ETH_LINK_DOWN</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0131149</t>
+          <t>0130903</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0131149_LM_Nuevo_Caqueta</t>
+          <t>0130903_AQ_El_Palomar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>01:42:31</t>
+          <t>05:57:02</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RIMAC</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>dispatched</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Ivan Bueno</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-20 11:50:42</t>
+          <t>2026-08-26 10:42:39</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>dispatch</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>JERSON ALBERTO SOTO LARICO</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -724,24 +724,24 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CM-20260820-00000048</t>
+          <t>CM-20260826-00000075</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INC-20260820-00001382</t>
+          <t>INC-20260826-00002621</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-20 04:52:31</t>
+          <t>2026-08-26 10:16:50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 10:18:37</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>26234-BBU CPRI Interface Error</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0135261</t>
+          <t>0130387</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0135261_LM_Los_Incas</t>
+          <t>0130387_LM_Lurin</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ACC PERDIDA GESTION_HW FAULT</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>08:38:30</t>
+          <t>06:21:27</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -816,22 +816,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>COMAS</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-20 04:54:43</t>
+          <t>2026-08-26 10:18:14</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
+          <t/>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -896,54 +896,54 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CM-20260820-00000022</t>
+          <t>CM-20260826-00000061</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INC-20260820-00000473</t>
+          <t>INC-20260826-00002028</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-20 01:31:51</t>
+          <t>2026-08-26 09:08:42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-20 10:28:01</t>
+          <t/>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-20 10:28:01</t>
+          <t>2026-08-26 15:15:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>772907009-The feeder fiber is broken or OLT can not receive any expected optical signals (LOS)</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>prueba</t>
+          <t/>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0130266</t>
+          <t>0130396</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0130266_LM_Bausate</t>
+          <t>0130396_LM_Mal_Paso</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>11:24:40</t>
+          <t>07:29:02</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -988,27 +988,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>CAÑETE</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Martín Figueroa</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-20 02:08:33</t>
+          <t>2026-08-26 09:10:39</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1018,9 +1018,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:Henrry.Navarro
-Complete time: 2026-08-20 10:23:35
-Description: Hilos atenuado en mufs </t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1035,12 +1033,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>JOHAN  HUAYHUARIMA LEON</t>
+          <t/>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1050,17 +1048,17 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-20 10:23:39</t>
+          <t/>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2026-08-20 10:24:28</t>
+          <t/>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-08-20 10:24:33</t>
+          <t/>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1075,39 +1073,39 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CM-20260819-00000187</t>
+          <t>CM-20260825-00000253</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INC-20260819-00005479</t>
+          <t>INC-20260825-00006049</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:40:43</t>
+          <t>2026-08-25 18:22:13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 18:31:54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1132,17 +1130,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>015252733</t>
+          <t>0130103</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>015252733_LM_NR_Diez_Canseco_AMT</t>
+          <t>0130103_LM_Wiracocha</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1157,7 +1155,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>23:50:21</t>
+          <t>22:15:18</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,22 +1170,22 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>MIRAFLORES</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:42:52</t>
+          <t>2026-08-25 18:24:23</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1242,7 +1240,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 18:31:54</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1252,29 +1250,29 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CM-20260819-00000165</t>
+          <t>CM-20260825-00000250</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INC-20260819-00003480</t>
+          <t>INC-20260825-00005923</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-19 10:50:05</t>
+          <t>2026-08-25 18:08:19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1294,7 +1292,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>12793-ETH_LINK_DOWN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1309,12 +1307,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0130811</t>
+          <t>0135592</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0130811_IC_Ocucaje</t>
+          <t>0135592_LM_Ucayali_America</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1324,47 +1322,47 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>01:05:23</t>
+          <t>22:30:44</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Ronald Abarca</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-19 12:27:50</t>
+          <t>2026-08-25 18:08:57</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1389,12 +1387,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+          <t/>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1429,7 +1427,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1441,37 +1439,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CM-20260819-00000151</t>
+          <t>CM-20260825-00000248</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INC-20260819-00004268</t>
+          <t>INC-20260825-00005893</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-19 12:01:30</t>
+          <t>2026-08-25 18:03:48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 11:56:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 11:56:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1-R_LOS</t>
+          <t>12793-ETH_LINK_DOWN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1486,32 +1484,32 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0130442</t>
+          <t>0130107</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0130442_LM_Los_Alamos</t>
+          <t>0130107_LM_Higuereta</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>01:29:39</t>
+          <t>22:34:53</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1526,22 +1524,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>SANTIAGO DE SURCO</t>
+          <t>SURQUILLO</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>inprocess</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-19 12:03:34</t>
+          <t>2026-08-25 18:04:48</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1566,12 +1564,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>arrive</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+          <t/>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1596,7 +1594,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 11:53:34</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1618,22 +1616,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CM-20260819-00000145</t>
+          <t>CM-20260825-00000233</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INC-20260819-00004069</t>
+          <t>INC-20260825-00005523</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-19 11:41:46</t>
+          <t>2026-08-25 16:52:09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:54:00</t>
+          <t>2026-08-26 04:42:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1643,37 +1641,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:54:00</t>
+          <t>2026-08-26 03:06:47</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Access Issue</t>
+          <t/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0131295</t>
+          <t>0135205</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0131295_LM_Sucre_Llosa</t>
+          <t>0135205_LM_Cantera_Cieneguilla</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1683,12 +1681,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>01:49:14</t>
+          <t>23:45:03</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1703,7 +1701,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>MAGDALENA DEL MAR</t>
+          <t>CIENEGUILLA</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1713,24 +1711,33 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Yoshua Quispe</t>
+          <t>Martín Figueroa</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-19 11:43:59</t>
+          <t>2026-08-25 16:54:38</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Type: PAUSE
+Reason: Otros
+Operation time: 2026-08-25 18:23:13
+Creator: aramirez.cobra
+Description: zona insegura 
+Type: RESUME
+Reason: 
+Operation time: 2026-08-26 04:31:17
+Creator: aramirez.cobra
+Description: se recupera reserva de cable y se vuelve a conectar los hilos </t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Operator: user:bcastillod
-Complete time: 2026-08-19 15:49:42
-Description: se hizo cambio de hilo entre mufa ( la primera es la mufa principal del site Llosa y una anterior a esa )</t>
+          <t xml:space="preserve">Operator: user:System
+Complete time: 2026-08-26 04:37:28
+Description: se recupera reserva de cable y se vuelve a conectar los hilos en la mufa existe en dónde se conecxiiona todo ok </t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1750,7 +1757,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t>ALEJANDRO JOSE GREGORIO RAMIREZ</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1760,17 +1767,17 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:49:44</t>
+          <t>2026-08-26 04:37:30</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:50:11</t>
+          <t>2026-08-26 04:39:47</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:50:14</t>
+          <t>2026-08-26 04:39:48</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1785,49 +1792,49 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CM-20260818-00000206</t>
+          <t>CM-20260825-00000191</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INC-20260818-00006078</t>
+          <t>INC-20260825-00004775</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-18 14:00:51</t>
+          <t>2026-08-25 14:52:29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-19 06:34:00</t>
+          <t/>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-19 06:34:00</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1837,22 +1844,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0135534</t>
+          <t>0130028</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0135534_LM_Nuevo_San_Juan</t>
+          <t>0130028_LM_MSO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1867,7 +1874,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>23:29:08</t>
+          <t>01:45:24</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1882,37 +1889,51 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>inprocess</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-18 14:04:05</t>
+          <t>2026-08-25 14:54:17</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Type: PAUSE
+Reason: SLAAutoPaused
+Operation time: 2026-08-26 10:59:50
+Creator: jhuayhuarima.cobra
+Description: Pausa por asignacion 
+Type: RESUME
+Reason: 
+Operation time: 2026-08-26 15:52:22
+Creator: janastacio.cobra
+Description: en camino a revisión de averia 
+Type: PAUSE
+Reason: Otros
+Operation time: 2026-08-26 15:52:40
+Creator: janastacio.cobra
+Description: pausa</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:vcauti.cobra
+          <t xml:space="preserve">Operator: user:jhuayhuarima.cobra
 Complete time: 
 Description: 
-Operator: user:daniel.reano
-Complete time: 2026-08-19 06:26:46
-Description:  se encuentra corte. y se empalma </t>
+Operator: user:janastacio.cobra
+Complete time: 
+Description: </t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1927,32 +1948,32 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>depart</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-19 06:26:48</t>
+          <t/>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2026-08-19 06:31:32</t>
+          <t/>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-08-19 06:31:34</t>
+          <t/>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1967,54 +1988,54 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CM-20260818-00000193</t>
+          <t>CM-20260825-00000174</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INC-20260818-00005964</t>
+          <t>INC-20260825-00004424</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-18 13:37:50</t>
+          <t>2026-08-25 13:58:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-19 00:06:00</t>
+          <t/>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18 20:13:46</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2024,17 +2045,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0135125</t>
+          <t>0130193</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0135125_LM_Los_Heroes</t>
+          <t>0130193_LM_Mirones</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2049,7 +2070,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>23:54:55</t>
+          <t>02:22:37</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2064,34 +2085,41 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>dispatched</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-18 13:38:18</t>
+          <t>2026-08-25 14:17:04</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Type: PAUSE
+Reason: Otros
+Operation time: 2026-08-26 12:31:10
+Creator: gchumbe.cobra
+Description: otros</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Operator: user:System
-Complete time: 2026-08-19 00:02:20
-Description: hilo quebrado, se hace cambio de hilo</t>
+          <t xml:space="preserve">Operator: user:gchumbe.cobra
+Complete time: 
+Description: 
+Operator: user:eatencio.cobra
+Complete time: 
+Description: </t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2106,32 +2134,32 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+          <t>EDENSON BRAYEN ATENCIO ARAGON</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-19 00:02:22</t>
+          <t/>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2026-08-19 00:03:50</t>
+          <t/>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-08-19 00:03:57</t>
+          <t/>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -2146,54 +2174,54 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CM-20260818-00000126</t>
+          <t>CM-20260825-00000113</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INC-20260818-00003184</t>
+          <t>INC-20260825-00002763</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-18 08:53:24</t>
+          <t>2026-08-25 10:20:38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 16:00:18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 21:13:35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2505224-Optical Invalid</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2203,12 +2231,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0130054</t>
+          <t>0130302</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0130054_LM_Curie</t>
+          <t>0130302_LM_Comercial_Surquill</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2218,17 +2246,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ATENUADO</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>04:38:31</t>
+          <t>06:16:38</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2243,22 +2271,22 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>SURQUILLO</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-18 08:54:42</t>
+          <t>2026-08-25 10:23:03</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2268,9 +2296,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:System
+          <t xml:space="preserve">Operator: user:janastacio.cobra
 Complete time: 
-Description: </t>
+Description: 
+Operator: user:System
+Complete time: 2026-08-26 15:51:37
+Description: se corrige hilo quebrado </t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2285,12 +2316,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t/>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2300,17 +2331,17 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 15:51:39</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 15:52:00</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26 15:52:03</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2337,17 +2368,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CM-20260818-00000127</t>
+          <t>CM-20260825-00000027</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INC-20260818-00003184</t>
+          <t>INC-20260825-00000715</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-18 08:53:24</t>
+          <t>2026-08-25 02:30:14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2362,12 +2393,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 13:33:11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2505224-Optical Invalid</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2382,32 +2413,32 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0130054</t>
+          <t>0136063</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0130054_LM_Curie</t>
+          <t>0136063_LM_Felipe_Villaran</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ATENUADO</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>04:38:36</t>
+          <t>14:07:18</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2422,22 +2453,22 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-18 08:54:37</t>
+          <t>2026-08-25 02:32:23</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2492,7 +2523,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-08-18 08:55:13</t>
+          <t/>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2502,29 +2533,29 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CM-20260818-00000087</t>
+          <t>CM-20260825-00000012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INC-20260818-00002278</t>
+          <t>INC-20260825-00000236</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-18 06:19:34</t>
+          <t>2026-08-25 00:44:34</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2539,12 +2570,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18 10:23:34</t>
+          <t>2026-08-26 11:47:47</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2505070001-LD Input LOS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2559,17 +2590,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0135667</t>
+          <t>0130061</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0135667_LM_Betancourt</t>
+          <t>0130061_LM_San_Felipe</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2579,12 +2610,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>07:12:37</t>
+          <t>15:53:24</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2599,7 +2630,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>LOS OLIVOS</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2614,7 +2645,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-08-18 06:20:36</t>
+          <t>2026-08-25 00:46:17</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2691,42 +2722,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CM-20260818-00000065</t>
+          <t>CM-20260825-00000009</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INC-20260818-00001791</t>
+          <t>INC-20260825-00000073</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-18 04:31:36</t>
+          <t>2026-08-25 00:20:39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-18 08:41:10</t>
+          <t>2026-08-25 15:18:01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 15:18:01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2505070005-FIBER_CUT</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t/>
+          <t>Access Issue</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2736,12 +2767,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0130036</t>
+          <t>0130266</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0130036_LM_Rio_Nazca</t>
+          <t>0130266_LM_Bausate</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2751,17 +2782,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>GESTION</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>08:56:12</t>
+          <t>16:16:46</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2776,22 +2807,22 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-08-18 04:37:01</t>
+          <t>2026-08-25 00:22:55</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2801,7 +2832,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:gvivanco.cobra
+Complete time: 
+Description: 
+Operator: user:ENTEL09740786
+Complete time: 2026-08-25 15:13:22
+Description: se encuentra CTO con malos parámetros </t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2816,12 +2852,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t/>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2831,22 +2867,22 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 15:13:23</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 15:14:18</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 15:14:19</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-08-18 08:41:12</t>
+          <t/>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2856,7 +2892,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2868,17 +2904,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CM-20260817-00000292</t>
+          <t>CM-20260824-00000281</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INC-20260817-00008493</t>
+          <t>INC-20260824-00005976</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-17 21:35:26</t>
+          <t>2026-08-24 19:25:21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2893,12 +2929,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17 23:32:19</t>
+          <t>2026-08-25 07:58:42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2505274-Physical Port Down</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2913,12 +2949,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0130519</t>
+          <t>0130210</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0130519_LM_Montenegro</t>
+          <t>0130210_LM_San_Gabriel</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2933,12 +2969,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>15:56:39</t>
+          <t>20:17:23</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2953,34 +2989,38 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-08-17 21:36:34</t>
+          <t>2026-08-24 20:22:18</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Type: PAUSE
+Reason: Grupo Electrógeno Instalado
+Operation time: 2026-08-26 15:41:53
+Creator: eatencio.cobra
+Description: corte programado de fluido eléctrico de 11am a 20 pm</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t/>
@@ -2993,17 +3033,17 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t/>
+          <t>EDENSON BRAYEN ATENCIO ARAGON</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3033,44 +3073,44 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CM-20260817-00000281</t>
+          <t>CM-20260824-00000216</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INC-20260817-00008246</t>
+          <t>INC-20260824-00004590</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-17 20:56:20</t>
+          <t>2026-08-24 15:47:48</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-17 21:02:27</t>
+          <t>2026-08-25 09:08:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 09:08:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3080,7 +3120,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3090,17 +3130,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>013140328</t>
+          <t>0130135</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>013140328_AQ_Puente_Anashuayco</t>
+          <t>0130135_LM_Garcia_y_Garcia</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3115,37 +3155,37 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>16:34:33</t>
+          <t>00:21:02</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>CERRO COLORADO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Ivan Bueno</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-08-17 20:58:40</t>
+          <t>2026-08-24 16:18:39</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -3155,7 +3195,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:eatencio.cobra
+Complete time: 
+Description: 
+Operator: user:ENTEL09740786
+Complete time: 2026-08-25 09:05:32
+Description: Fibra Optica atenuada</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3170,12 +3215,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t/>
+          <t>EDENSON BRAYEN ATENCIO ARAGON</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3185,22 +3230,22 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 09:05:34</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 09:05:56</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-25 09:05:58</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-08-17 21:02:27</t>
+          <t/>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -3210,34 +3255,34 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CM-20260817-00000175</t>
+          <t>CM-20260824-00000081</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INC-20260817-00004339</t>
+          <t>INC-20260824-00001433</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:37</t>
+          <t>2026-08-24 07:09:44</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-18 01:22:00</t>
+          <t>2026-08-25 10:12:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3247,42 +3292,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-17 14:10:51</t>
+          <t>2026-08-24 10:38:29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
+          <t>2601500-ETH_LOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0162733</t>
+          <t>0130028</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0162733_LM_HB_Diez_Canseco_AMT</t>
+          <t>0130028_LM_MSO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3292,7 +3337,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>23:45:53</t>
+          <t>09:28:35</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3322,19 +3367,40 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-08-17 13:47:20</t>
+          <t>2026-08-24 07:11:06</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Type: PAUSE
+Reason: Pandemias
+Operation time: 2026-08-24 21:14:48
+Creator: janastacio.cobra
+Description: otros
+Type: RESUME
+Reason: 
+Operation time: 2026-08-25 09:02:53
+Creator: vcauti.cobra
+Description: se ubica corte </t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Operator: user:cesil.bustamante
-Complete time: 2026-08-18 01:17:28
-Description: atenuacion</t>
+          <t xml:space="preserve">Operator: user:eatencio.cobra
+Complete time: 
+Description: 
+Operator: user:jcarrion.cobra
+Complete time: 
+Description: 
+Operator: user:janastacio.cobra
+Complete time: 
+Description: 
+Operator: user:vcauti.cobra
+Complete time: 
+Description: 
+Operator: user:System
+Complete time: 2026-08-25 10:08:54
+Description:  se   permuta hilo </t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3354,7 +3420,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>EDENSON BRAYEN ATENCIO ARAGON</t>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3364,17 +3430,17 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-18 01:17:29</t>
+          <t>2026-08-25 10:08:56</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2026-08-18 01:18:18</t>
+          <t>2026-08-25 10:09:48</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-08-18 01:18:22</t>
+          <t>2026-08-25 10:09:50</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3389,214 +3455,366 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CM-20260817-00000171</t>
+          <t>CM-20260824-00000006</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INC-20260817-00004515</t>
+          <t>INC-20260824-00000084</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-17 13:25:18</t>
+          <t>2026-08-24 00:19:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-18 17:28:01</t>
+          <t/>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:14:40</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>235-ETH_LOS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0134528</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0134528_LM_Vilcahuaura</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>16:19:14</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>HUAURA</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Yoshua Quispe</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:20:27</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CM-20260823-00000360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INC-20260823-00006213</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-23 19:59:34</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:46:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-18 16:34:21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1100466-OSPF Interface State Changed</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>FO Cut</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0130032</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0130032_LM_Jorge_Chavez</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:46:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>32-IN_PWR_LOW</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Transmission</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0130522</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0130522_LM_IB_MSO_San_Borja</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>P0+</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ATENUADO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>23:51:47</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>20:36:21</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>SAN BORJA</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Edwin Oscco</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2026-08-17 13:41:26</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Type: PAUSE
-Reason: Otros
-Operation time: 2026-08-17 17:36:45
-Creator: janastacio.cobra
-Description: prioridad a otro caso 
-Type: RESUME
-Reason: 
-Operation time: 2026-08-18 03:33:51
-Creator: aramirez.cobra
-Description: continuación del trabajo 
-Type: PAUSE
-Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
-Operation time: 2026-08-18 03:40:00
-Creator: aramirez.cobra
-Description: por ser trabajo de madrugada serenazgo no permite continuar con el trabajo 
-Type: RESUME
-Reason: 
-Operation time: 2026-08-18 17:21:04
-Creator: gaquije.cobra
-Description: se continuo el trabajo asignado se concediendo permisos</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Operator: user:aramirez.cobra
-Complete time: 
-Description: 
-Operator: user:gaquije.cobra
-Complete time: 
-Description: 
-Operator: user:cesil.bustamante
-Complete time: 2026-08-18 17:24:02
-Description: se siguió el hilo. estaba partido en mufa, se empalmo y levantó el servicio</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Álvaro Ballarta</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:03:20</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator: user:Henrry.Navarro
+Complete time: 2026-08-24 07:42:56
+Description: fibra Atenuado, se realiza limpieza </t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2026-08-18 17:24:04</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>2026-08-18 17:24:55</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2026-08-18 17:24:57</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:42:58</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:43:27</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:43:29</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>00:03:26</t>
+          <t>01:32:37</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>00:42:33</t>
+          <t>02:11:44</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>02:03:43</t>
+          <t>03:32:54</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>04:09:05</t>
+          <t>05:38:16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>12:23:21</t>
+          <t>13:52:32</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>00:47:18</t>
+          <t>02:16:29</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>02:41:17</t>
+          <t>04:10:28</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>03:37:34</t>
+          <t>05:06:45</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10:38:54</t>
+          <t>12:08:05</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15:47:16</t>
+          <t>17:16:27</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17:45:44</t>
+          <t>19:14:55</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>01:14:23</t>
+          <t>02:43:34</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>04:33:20</t>
+          <t>06:02:31</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>04:57:45</t>
+          <t>06:26:56</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>06:05:20</t>
+          <t>07:34:31</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20:51:36</t>
+          <t>22:20:47</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21:07:02</t>
+          <t>22:36:13</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>21:11:11</t>
+          <t>22:40:22</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>22:21:21</t>
+          <t>23:50:32</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>03:21:05</t>
+          <t>03:50:41</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>07:34:51</t>
+          <t>08:04:27</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>09:45:05</t>
+          <t>10:14:41</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>05:27:07</t>
+          <t>05:56:43</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>03:16:58</t>
+          <t>03:46:34</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>04:42:22</t>
+          <t>05:11:58</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>06:43:28</t>
+          <t>07:13:04</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14:29:39</t>
+          <t>14:59:15</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>15:34:59</t>
+          <t>16:04:35</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>16:16:46</t>
+          <t>16:46:22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>20:20:57</t>
+          <t>20:50:33</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2328,200 +2328,6 @@
         </is>
       </c>
       <c r="AI12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CM-20260828-00000245</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>INC-20260828-00006142</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-08-28 17:51:20</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:40:00</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-29 21:56:25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>FO Cut</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0130522</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0130522_LM_IB_MSO_San_Borja</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>P0+</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>23:37:47</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>SAN BORJA</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-08-28 17:55:32</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type: PAUSE
-Reason: SLAAutoPaused
-Operation time: 2026-08-29 04:16:16
-Creator: aramirez.cobra
-Description: falta validar número de puerto para el enlace 
-Type: RESUME
-Reason: 
-Operation time: 2026-08-29 12:41:47
-Creator: mhuayanab.ofg
-Description: alarma presente </t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Operator: user:gvivanco.cobra
-Complete time: 
-Description: 
-Operator: user:janastacio.cobra
-Complete time: 
-Description: 
-Operator: user:cesil.bustamante
-Complete time: 2026-08-29 23:36:07
-Description: HILO QUEBRADO EN MUFA POR MANIPULACIÓN, SE HACE CAMBIO DE HILO ENTRE MUFAS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:36:09</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:37:00</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2026-08-29 23:37:02</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -377,17 +377,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CM-20260902-00000235</t>
+          <t>CM-20260907-00000223</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INC-20260902-00005392</t>
+          <t>INC-20260907-00005974</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:09:06</t>
+          <t>2026-09-07 18:44:42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2506110004-Cell Unavailable Transporte</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -422,12 +422,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0136188</t>
+          <t>0130045</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0136188_LM_Kamana_Villa</t>
+          <t>0130045_LM_Shell</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -437,7 +437,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ACC DEGRADACION_HW FAULT</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>00:53:29</t>
+          <t>13:46:25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -462,34 +462,38 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>PACHACAMAC</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:39:35</t>
+          <t>2026-09-07 18:46:53</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Type: PAUSE
+Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
+Operation time: 2026-09-07 22:18:48
+Creator: vcauti.cobra
+Description: serenasgo no permite el trabajo hora  de trabajo permitido 9:00 a 17:00 hrs</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t/>
@@ -502,17 +506,17 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t/>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -542,7 +546,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -554,42 +558,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CM-20260902-00000234</t>
+          <t>CM-20260907-00000194</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INC-20260902-00005392</t>
+          <t>INC-20260907-00005030</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:09:06</t>
+          <t>2026-09-07 15:49:02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:08:09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:08:09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2506110004-Cell Unavailable Transporte</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t/>
+          <t>Rectifier</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -599,12 +603,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0136188</t>
+          <t>0130176</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0136188_LM_Kamana_Villa</t>
+          <t>0130176_LM_Huanuco</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -624,7 +628,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>01:22:46</t>
+          <t>16:41:23</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -639,22 +643,22 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>PACHACAMAC</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:10:18</t>
+          <t>2026-09-07 15:51:55</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -664,7 +668,9 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:bcastillod
+Complete time: 2026-09-07 18:04:27
+Description: atenuación en el empalme a 166 mtrs en una mufa</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -679,12 +685,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -694,17 +700,17 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:04:29</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:05:23</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:05:24</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -719,54 +725,54 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CM-20260902-00000054</t>
+          <t>CM-20260907-00000078</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INC-20260902-00001294</t>
+          <t>INC-20260907-00002481</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-02 07:16:46</t>
+          <t>2026-09-07 09:50:11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:14:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:14:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>12793-ETH_LINK_DOWN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -776,22 +782,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0135354</t>
+          <t>0130266</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0135354_LM_Los_Jasmines</t>
+          <t>0130266_LM_Bausate</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -801,7 +807,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>10:14:40</t>
+          <t>22:42:14</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -816,22 +822,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-02 07:18:24</t>
+          <t>2026-09-07 09:51:04</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,7 +847,9 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:jose.cuya
+Complete time: 2026-09-07 18:10:29
+Description: atenuación a 166 mtrs, se rehace el empalme en mufa </t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -856,12 +864,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>JORGE GERMAN PACHECO MARTINEZ</t>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -871,17 +879,17 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:10:31</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:10:56</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 18:10:58</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -896,29 +904,29 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CM-20260902-00000013</t>
+          <t>CM-20260907-00000076</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INC-20260902-00000203</t>
+          <t>INC-20260907-00002334</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:11:17</t>
+          <t>2026-09-07 09:25:16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -948,22 +956,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0135657</t>
+          <t>0135774</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0135657_LM_Central_Independenc</t>
+          <t>0135774_LM_Lima_Centro</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -978,7 +986,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>16:19:46</t>
+          <t>23:02:35</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -993,32 +1001,41 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Yoshua Quispe</t>
+          <t>Edgar Soto</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:13:18</t>
+          <t>2026-09-07 09:30:43</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Type: PAUSE
+Reason: Restricciones por temas de seguridad personal
+Operation time: 2026-09-07 18:10:27
+Creator: jhuayhuarima.cobra
+Description: Cámara a inspecciónar en vía con exceso transito vehicular </t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:janastacio.cobra
+Complete time: 
+Description: 
+Operator: user:jhuayhuarima.cobra
+Complete time: 
+Description: </t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1033,17 +1050,17 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>JORGE GERMAN PACHECO MARTINEZ</t>
+          <t>JOHAN  HUAYHUARIMA LEON</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1085,42 +1102,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CM-20260901-00000278</t>
+          <t>CM-20260907-00000051</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INC-20260901-00006520</t>
+          <t>INC-20260907-00001641</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-01 18:53:01</t>
+          <t>2026-09-07 07:00:26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 13:58:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:00:45</t>
+          <t>2026-09-07 07:58:51</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2505274-Physical Port Down</t>
+          <t>772907009-The feeder fiber is broken or OLT can not receive any expected optical signals (LOS)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t/>
+          <t>prueba</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1130,17 +1147,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0130149</t>
+          <t>0130136</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0130149_LM_Trapiche</t>
+          <t>0130136_LM_Bolivia</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1150,12 +1167,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>22:35:09</t>
+          <t>01:24:06</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1170,22 +1187,22 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>COMAS</t>
+          <t>BREÑA</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-01 18:57:55</t>
+          <t>2026-09-07 07:09:12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1195,7 +1212,9 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:Boris.Chivilchez
+Complete time: 2026-09-07 13:54:57
+Description: Se tiene valores en naps</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1210,12 +1229,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t/>
+          <t>JOHAN  HUAYHUARIMA LEON</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1225,17 +1244,17 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 13:55:02</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 13:55:28</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 13:55:33</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1250,7 +1269,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1262,42 +1281,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CM-20260901-00000267</t>
+          <t>CM-20260907-00000040</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INC-20260901-00006399</t>
+          <t>INC-20260907-00001335</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-01 18:33:37</t>
+          <t>2026-09-07 05:45:08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 15:50:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 06:36:08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12793-ETH_LINK_DOWN</t>
+          <t>2505274-Physical Port Down</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>Rectifier</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1307,17 +1326,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0130499</t>
+          <t>0130119</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0130499_LM_Huarochiri</t>
+          <t>0130119_LM_Estadio_Alianza</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1327,12 +1346,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22:58:45</t>
+          <t>02:27:50</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1347,22 +1366,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>SANTA ANITA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Yoshua Quispe</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-01 18:34:19</t>
+          <t>2026-09-07 06:05:28</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1372,7 +1391,9 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:Boris.Chivilchez
+Complete time: 2026-09-07 15:46:07
+Description: se hizo pruebas de potencia y traza, queda limpio de site a site</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1387,12 +1408,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t/>
+          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1402,17 +1423,17 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 15:46:09</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 15:47:07</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 15:47:09</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1427,29 +1448,29 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CM-20260901-00000205</t>
+          <t>CM-20260906-00000274</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INC-20260901-00004972</t>
+          <t/>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:46:41</t>
+          <t/>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1459,7 +1480,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>running</t>
+          <t/>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1469,7 +1490,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2507160006-ETH_LOS_Caida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1484,22 +1505,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0134626</t>
+          <t>0130028</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0134626_LM_Mso_Entel</t>
+          <t>0130028_LM_MSO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1509,7 +1530,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>02:44:35</t>
+          <t>15:10:04</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1524,22 +1545,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>SAN BORJA</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:48:29</t>
+          <t>2026-09-06 17:23:14</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1564,12 +1585,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+          <t/>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1604,7 +1625,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1616,37 +1637,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CM-20260901-00000204</t>
+          <t>CM-20260906-00000161</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INC-20260901-00004972</t>
+          <t>INC-20260906-00002573</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-01 14:46:41</t>
+          <t>2026-09-06 10:15:11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-06 11:16:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-06 10:24:57</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29240-Cell Unavailable</t>
+          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1656,17 +1677,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0134626</t>
+          <t>0130136</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0134626_LM_Mso_Entel</t>
+          <t>0130136_LM_Bolivia</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1676,7 +1697,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ACC FALLO RED TEC_AFECTACION NODO</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1686,7 +1707,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>02:44:44</t>
+          <t>22:09:29</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1701,7 +1722,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>SAN BORJA</t>
+          <t>BREÑA</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1711,12 +1732,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-01 14:48:20</t>
+          <t>2026-09-06 10:23:49</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1771,7 +1792,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-01 14:48:55</t>
+          <t>2026-09-06 11:13:37</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1781,7 +1802,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1793,17 +1814,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CM-20260901-00000181</t>
+          <t>CM-20260906-00000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INC-20260901-00004510</t>
+          <t>INC-20260906-00000362</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-01 13:44:45</t>
+          <t>2026-09-06 01:23:26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1818,12 +1839,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-06 14:44:04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2505224-Optical Invalid</t>
+          <t>2505070002-Input LOS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1838,32 +1859,32 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0135774</t>
+          <t>0130377</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0135774_LM_Lima_Centro</t>
+          <t>0130377_LM_Huaral</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ATENUADO</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>03:47:38</t>
+          <t>07:09:02</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1873,12 +1894,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1888,12 +1909,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-01 13:45:26</t>
+          <t>2026-09-06 01:24:16</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1958,7 +1979,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -1970,17 +1991,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CM-20260901-00000176</t>
+          <t>CM-20260905-00000337</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INC-20260901-00004314</t>
+          <t>INC-20260905-00008460</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-01 13:16:06</t>
+          <t>2026-09-05 21:57:23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2000,7 +2021,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2508200002-ETH_LOS_CAIDA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2010,37 +2031,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0130094</t>
+          <t>0135261</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0130094_LM_El_Pino</t>
+          <t>0135261_LM_Los_Incas</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>04:07:42</t>
+          <t>10:34:29</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2055,7 +2076,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>COMAS</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2065,12 +2086,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Martín Figueroa</t>
+          <t>César Zuñiga</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-01 13:25:22</t>
+          <t>2026-09-05 21:58:49</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -2080,7 +2101,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:janastacio.cobra
+          <t xml:space="preserve">Operator: user:lgarcia.ofg
 Complete time: 
 Description: </t>
         </is>
@@ -2102,7 +2123,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
+          <t>LEONARDO DAVID GARCIA PEREDA</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2149,62 +2170,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CM-20260901-00000132</t>
+          <t>CM-20260905-00000313</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INC-20260901-00003733</t>
+          <t>INC-20260905-00007588</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-01 11:53:16</t>
+          <t>2026-09-05 19:27:57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 01:46:10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 01:46:10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>1-R_LOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0130449</t>
+          <t>0130903</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0130449_LM_Pq_Ind_Lurin</t>
+          <t>0130903_AQ_El_Palomar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0+</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2214,42 +2235,42 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>05:37:01</t>
+          <t>13:04:10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>LURIN</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Ivan Bueno</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-01 11:56:03</t>
+          <t>2026-09-05 19:29:08</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2259,9 +2280,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator: user:jhuayhuarima.cobra
+          <t xml:space="preserve">Operator: user:janastacio.cobra
 Complete time: 
-Description: </t>
+Description: 
+Operator: user:Yuliza.Jaimes
+Complete time: 2026-09-08 01:42:36
+Description: SE UBICA HILO QUEBRADO EN MUFA </t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2276,12 +2300,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>JOHAN  HUAYHUARIMA LEON</t>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2291,17 +2315,17 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 01:42:37</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 01:43:06</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 01:43:08</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2328,17 +2352,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CM-20260901-00000072</t>
+          <t>CM-20260905-00000305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INC-20260901-00002388</t>
+          <t/>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-01 09:02:04</t>
+          <t/>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2348,17 +2372,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>running</t>
+          <t/>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-01 16:33:53</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12793-ETH_LINK_DOWN</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2373,32 +2397,32 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0130415</t>
+          <t>0130176</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0130415_LM_Candia</t>
+          <t>0130176_LM_Huanuco</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>08:28:20</t>
+          <t>13:47:43</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2413,12 +2437,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>SANTIAGO DE SURCO</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>dispatched</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2428,7 +2452,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-01 09:04:44</t>
+          <t>2026-09-05 18:45:35</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2453,12 +2477,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>dispatch</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t/>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2505,42 +2529,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CM-20260901-00000013</t>
+          <t>CM-20260905-00000258</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INC-20260901-00000269</t>
+          <t>INC-20260905-00004788</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-01 00:45:32</t>
+          <t>2026-09-05 12:37:46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:24:00</t>
+          <t/>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:31:39</t>
+          <t>2026-09-05 12:41:40</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2505274-Physical Port Down</t>
+          <t>4-GNE_CONNECT_FAIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>prueba</t>
+          <t/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2550,32 +2574,32 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0130119</t>
+          <t>0130478</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0130119_LM_Estadio_Alianza</t>
+          <t>0130478_LM_Tiahuanaco</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>DEGRADACION</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>16:41:42</t>
+          <t>17:18:59</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2590,22 +2614,22 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Yoshua Quispe</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-09-01 00:51:22</t>
+          <t>2026-09-05 15:14:19</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2615,12 +2639,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Operator: user:jhuayhuarima.cobra
-Complete time: 
-Description: 
-Operator: user:Yuliza.Jaimes
-Complete time: 2026-09-01 15:17:21
-Description: Fibra partida</t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2635,12 +2654,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>JOHAN  HUAYHUARIMA LEON</t>
+          <t/>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2650,17 +2669,17 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:20:19</t>
+          <t/>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:35</t>
+          <t/>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:20:22</t>
+          <t/>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2687,42 +2706,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CM-20260831-00000287</t>
+          <t>CM-20260905-00000204</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INC-20260831-00006075</t>
+          <t>INC-20260905-00004648</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-31 22:39:06</t>
+          <t>2026-09-05 12:25:19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:42:00</t>
+          <t/>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31 22:39:28</t>
+          <t>2026-09-05 23:11:54</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2507160001-ETH_LOS_CAIDA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>FO Cut</t>
+          <t/>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2732,32 +2751,32 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0135132</t>
+          <t>0136188</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0135132_LM_Eloy_Ureta</t>
+          <t>0136188_LM_Kamana_Villa</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>18:50:03</t>
+          <t>19:35:12</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2772,47 +2791,32 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
+          <t>PACHACAMAC</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Álvaro Ballarta</t>
+          <t>Martín Figueroa</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-08-31 22:43:01</t>
+          <t>2026-09-05 12:58:06</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type: PAUSE
-Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
-Operation time: 2026-09-01 07:14:51
-Creator: aramirez.cobra
-Description: se toma medidas desde la antena y se colocó luz hasta la mufa en dónde no encuentro la luz 
-Type: RESUME
-Reason: 
-Operation time: 2026-09-01 16:22:54
-Creator: gaquije.cobra
-Description: continuamos trabajos
-</t>
+          <t>'-</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Operator: user:gaquije.cobra
-Complete time: 
-Description: 
-Operator: user:cesil.bustamante
-Complete time: 2026-09-01 16:37:27
-Description: hilos partidos en bandejas intermedias</t>
+          <t>'-</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2827,12 +2831,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
+          <t/>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2842,17 +2846,17 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:37:28</t>
+          <t/>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:39:03</t>
+          <t/>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:39:05</t>
+          <t/>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2879,42 +2883,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CM-20260831-00000155</t>
+          <t>CM-20260905-00000202</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INC-20260831-00003784</t>
+          <t>INC-20260905-00004880</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-31 14:10:02</t>
+          <t>2026-09-05 12:44:52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 14:38:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-06 00:42:34</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1100299-Interface Loss of Signal</t>
+          <t>2505070002-Input LOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2939,7 +2943,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2949,7 +2953,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>03:20:50</t>
+          <t>19:47:30</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2969,7 +2973,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2979,7 +2983,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-08-31 14:12:14</t>
+          <t>2026-09-05 12:45:48</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2989,7 +2993,9 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:cesil.bustamante
+Complete time: 2026-09-07 14:33:45
+Description: se cablea nueva fo y se instalan 2 mufas </t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3004,12 +3010,12 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t/>
+          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3019,17 +3025,17 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 14:33:47</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 14:35:38</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07 14:35:40</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -3044,366 +3050,10 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CM-20260831-00000078</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>INC-20260831-00002175</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-08-31 09:56:16</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0135588</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0135588_LM_Trenemann</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>07:34:36</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Edgar Soto</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>2026-08-31 09:58:28</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CM-20260831-00000046</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>INC-20260831-00001559</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-08-31 07:45:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:30:01</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-31 14:28:58</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>prueba</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0130387</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0130387_LM_Lurin</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>09:44:50</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>LURIN</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Álvaro Ballarta</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2026-08-31 07:48:14</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Operator: user:Henrry.Navarro
-Complete time: 2026-08-31 14:59:34
-Description: Fibra partida en mufa se fusiona</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>JOHAN  HUAYHUARIMA LEON</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2026-08-31 14:59:37</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:00:00</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:00:03</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/scripts/WOs List PEXT.xlsx
+++ b/scripts/WOs List PEXT.xlsx
@@ -157,7 +157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="24" max="24" width="26.0" customWidth="true"/>
@@ -377,17 +377,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CM-20260908-00000205</t>
+          <t>CM-20260909-00000167</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INC-20260908-00005443</t>
+          <t>INC-20260909-00004101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-08 15:27:41</t>
+          <t>2026-09-09 13:07:36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>235-ETH_LOS</t>
+          <t>2601210001-Loss of signal</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -422,22 +422,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0130176</t>
+          <t>0130387</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0130176_LM_Huanuco</t>
+          <t>0130387_LM_Lurin</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CORTE</t>
+          <t>CAIDA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>01:02:29</t>
+          <t>04:24:23</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -462,22 +462,22 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>LURIN</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>dispatched</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>Álvaro Ballarta</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-08 15:30:44</t>
+          <t>2026-09-09 13:09:16</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dispatch</t>
+          <t>create</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RUBEN HILDO MERCADO CAMARGO</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -554,37 +554,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CM-20260908-00000169</t>
+          <t>CM-20260909-00000141</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INC-20260908-00004560</t>
+          <t>INC-20260909-00003294</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:44:55</t>
+          <t>2026-09-09 11:35:20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:55:08</t>
+          <t/>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>running</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:53:38</t>
+          <t>2026-09-09 16:39:16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2505070002-Input LOS</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0130011</t>
+          <t>0130415</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0130011_LM_Lurigancho</t>
+          <t>0130415_LM_Candia</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>02:47:14</t>
+          <t>05:56:40</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -639,22 +639,22 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LURIGANCHO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>inprocess</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Edgar Soto</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:59</t>
+          <t>2026-09-09 11:36:59</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>arrive</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:55:09</t>
+          <t/>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -719,54 +719,54 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CM-20260908-00000137</t>
+          <t>CM-20260909-00000105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>INC-20260909-00002322</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09 09:12:46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09 15:08:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>completed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09 14:07:51</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2507160001-ETH_LOS_CAIDA</t>
+          <t>2506110004-Cell Unavailable Transporte</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0136588</t>
+          <t>0135249</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0136588_LM_RepFO_Olguin_Amer</t>
+          <t>0135249_LM_Merino_Reyna</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>04:11:14</t>
+          <t>08:20:06</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -816,22 +816,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>SANTIAGO DE SURCO</t>
+          <t>CARABAYLLO</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Edwin Oscco</t>
+          <t>César Zuñiga</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-08 12:21:59</t>
+          <t>2026-09-09 09:13:33</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,7 +841,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t>Operator: user:gaquije.cobra
+Complete time: 
+Description: 
+Operator: user:cesil.bustamante
+Complete time: 2026-09-09 15:02:41
+Description: fibra partida en medio tramo</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -856,12 +861,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t/>
+          <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -871,17 +876,17 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09 15:02:42</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09 15:04:27</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09 15:04:28</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -896,7 +901,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -908,77 +913,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CM-20260908-00000104</t>
+          <t>CM-20260908-00000205</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INC-20260908-00003064</t>
+          <t>INC-20260908-00005443</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-08 10:40:49</t>
+          <t>2026-09-08 15:27:41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 18:02:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 18:02:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2506110004-Cell Unavailable Transporte</t>
+          <t>235-ETH_LOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t/>
+          <t>FO Cut</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0135261</t>
+          <t>0130176</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0135261_LM_Los_Incas</t>
+          <t>0130176_LM_Huanuco</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CAIDA</t>
+          <t>CORTE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>05:51:35</t>
+          <t>02:02:55</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -993,22 +998,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>COMAS</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>unscheduled</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>César Zuñiga</t>
+          <t>Edwin Oscco</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-08 10:41:38</t>
+          <t>2026-09-08 15:30:44</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1018,7 +1023,9 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>'-</t>
+          <t xml:space="preserve">Operator: user:bcastillod
+Complete time: 2026-09-08 17:57:34
+Description: Corte de fo, múltiples Llamadas </t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1033,12 +1040,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>close</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t/>
+          <t>RUBEN HILDO MERCADO CAMARGO</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1048,17 +1055,17 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 17:57:36</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 17:58:23</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08 17:58:24</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1073,7 +1080,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1085,289 +1092,820 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CM-20260908-00000169</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INC-20260908-00004560</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:44:55</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:55:08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cancel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:53:38</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2505070002-Input LOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0130011</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0130011_LM_Lurigancho</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CORTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>03:47:40</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Edgar Soto</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:45:59</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:55:09</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CM-20260908-00000137</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2507160001-ETH_LOS_CAIDA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0136588</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0136588_LM_RepFO_Olguin_Amer</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>05:11:40</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>unscheduled</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Edwin Oscco</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:21:59</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CM-20260908-00000104</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INC-20260908-00003064</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:40:49</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:31:26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2506110004-Cell Unavailable Transporte</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0135261</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0135261_LM_Los_Incas</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CAIDA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:52:01</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>dispatched</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>César Zuñiga</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:41:38</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>'-</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>O&amp;M PEXT</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dispatch</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>GERSON ANDRE VIVANCO DIESTRA</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>CM-20260908-00000087</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>INC-20260908-00002814</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-09-08 10:12:44</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026-09-08 14:34:01</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-09-08 13:31:47</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2506110004-Cell Unavailable Transporte</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>0135249</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0135249_LM_Merino_Reyna</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>CAIDA</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>06:19:41</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>07:20:07</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>CARABAYLLO</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>César Zuñiga</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>2026-09-08 10:13:32</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:cesil.bustamante
 Complete time: 2026-09-08 14:29:27
 Description: Fo reparada, empalmada </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>RUBEN HILDO MERCADO CAMARGO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>2026-09-08 14:29:30</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2026-09-08 14:30:12</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2026-09-08 14:30:13</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CM-20260907-00000223</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>INC-20260907-00005974</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-09-07 18:44:42</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026-09-08 11:10:00</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-09-08 11:10:01</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0130045</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0130045_LM_Shell</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>21:46:20</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>22:46:46</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MIRAFLORES</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Edwin Oscco</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>2026-09-07 18:46:53</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Type: PAUSE
 Reason: Restricciones de acceso por parte de terceros notificada a ENTEL
@@ -1381,7 +1919,7 @@
 Description: hilo alimentador roto</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:gvivanco.cobra
 Complete time: 
@@ -1391,532 +1929,532 @@
 Description: se encuentra hilo cortado a 1300 metros </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>2026-09-08 11:06:34</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2026-09-08 11:07:18</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2026-09-08 11:07:19</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CM-20260907-00000194</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>INC-20260907-00005030</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-09-07 15:49:02</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2026-09-07 18:08:09</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-09-07 18:08:09</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Rectifier</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>0130176</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0130176_LM_Huanuco</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>00:41:18</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>01:41:44</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>LA VICTORIA</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Edwin Oscco</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>2026-09-07 15:51:55</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Operator: user:bcastillod
 Complete time: 2026-09-07 18:04:27
 Description: atenuación en el empalme a 166 mtrs en una mufa</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>2026-09-07 18:04:29</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>2026-09-07 18:05:23</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2026-09-07 18:05:24</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CM-20260907-00000078</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>INC-20260907-00002481</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-09-07 09:50:11</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-09-07 18:14:00</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-09-07 18:14:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>12793-ETH_LINK_DOWN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>FO Cut</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0130266</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0130266_LM_Bausate</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>CAIDA</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>06:42:09</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>07:42:35</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>LA VICTORIA</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Edwin Oscco</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>2026-09-07 09:51:04</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:jose.cuya
 Complete time: 2026-09-07 18:10:29
 Description: atenuación a 166 mtrs, se rehace el empalme en mufa </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>GERSON ANDRE VIVANCO DIESTRA</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>2026-09-07 18:10:31</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2026-09-07 18:10:56</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2026-09-07 18:10:58</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CM-20260907-00000076</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>INC-20260907-00002334</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2026-09-07 09:25:16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-08 23:51:12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>235-ETH_LOS</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>0135774</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0135774_LM_Lima_Centro</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>07:02:30</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>08:02:56</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>accepted</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>dispatched</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>Edgar Soto</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>2026-09-07 09:30:43</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t xml:space="preserve">Type: PAUSE
 Reason: Restricciones por temas de seguridad personal
@@ -1925,1499 +2463,433 @@
 Description: Cámara a inspecciónar en vía con exceso transito vehicular </t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t xml:space="preserve">Operator: user:janastacio.cobra
 Complete time: 
 Description: 
 Operator: user:jhuayhuarima.cobra
 Complete time: 
+Description: 
+Operator: user:vcauti.cobra
+Complete time: 
 Description: </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>accept</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>JOHAN  HUAYHUARIMA LEON</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>CM-20260907-00000051</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>INC-20260907-00001641</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-09-07 07:00:26</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026-09-07 13:58:00</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-09-07 07:58:51</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>772907009-The feeder fiber is broken or OLT can not receive any expected optical signals (LOS)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>prueba</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>0130136</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0130136_LM_Bolivia</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>CAIDA</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>09:24:01</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10:24:27</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>BREÑA</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Yoshua Quispe</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>2026-09-07 07:09:12</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Operator: user:Boris.Chivilchez
 Complete time: 2026-09-07 13:54:57
 Description: Se tiene valores en naps</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>JOHAN  HUAYHUARIMA LEON</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>2026-09-07 13:55:02</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>2026-09-07 13:55:28</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>2026-09-07 13:55:33</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CM-20260907-00000040</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>INC-20260907-00001335</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-09-07 05:45:08</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026-09-07 15:50:00</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-09-07 06:36:08</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2505274-Physical Port Down</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Rectifier</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>0130119</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0130119_LM_Estadio_Alianza</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>CORTE</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>10:27:45</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>11:28:11</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>LIMA</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>LA VICTORIA</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Edwin Oscco</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>2026-09-07 06:05:28</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Operator: user:Boris.Chivilchez
 Complete time: 2026-09-07 15:46:07
 Description: se hizo pruebas de potencia y traza, queda limpio de site a site</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>O&amp;M PEXT</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>GABRIEL STTEFFANO AQUIJE CORNEJO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>2026-09-07 15:46:09</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>2026-09-07 15:47:07</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>2026-09-07 15:47:09</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CM-20260906-00000274</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2507160006-ETH_LOS_Caida</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0130028</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0130028_LM_MSO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>P0+</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>23:09:59</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Edwin Oscco</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-09-06 17:23:14</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CM-20260906-00000161</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>INC-20260906-00002573</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-09-06 10:15:11</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-06 11:16:00</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-06 10:24:57</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>772874247-The distribute fiber is broken or the OLT cannot receive expected optical signals from the ONT(LOSi LOBi)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0130136</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0130136_LM_Bolivia</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>06:09:24</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>BREÑA</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Yoshua Quispe</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-09-06 10:23:49</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>2026-09-06 11:13:37</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CM-20260906-00000009</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INC-20260906-00000362</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-09-06 01:23:26</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-09-08 09:03:52</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-06 14:44:04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2505070002-Input LOS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0130377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0130377_LM_Huaral</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>15:08:57</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>HUARAL</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>HUARAL</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>unscheduled</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Yoshua Quispe</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-09-06 01:24:16</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>create</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CM-20260905-00000337</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>INC-20260905-00008460</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-09-05 21:57:23</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2508200002-ETH_LOS_CAIDA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0135261</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0135261_LM_Los_Incas</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>CAIDA</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>18:34:24</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>COMAS</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>dispatched</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>César Zuñiga</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2026-09-05 21:58:49</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator: user:lgarcia.ofg
-Complete time: 
-Description: </t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>LEONARDO DAVID GARCIA PEREDA</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CM-20260905-00000313</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>INC-20260905-00007588</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-09-05 19:27:57</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-09-08 01:46:10</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-08 01:46:10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1-R_LOS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>FO Cut</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0130903</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0130903_AQ_El_Palomar</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>P0+</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>21:04:05</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Ivan Bueno</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>2026-09-05 19:29:08</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator: user:janastacio.cobra
-Complete time: 
-Description: 
-Operator: user:Yuliza.Jaimes
-Complete time: 2026-09-08 01:42:36
-Description: SE UBICA HILO QUEBRADO EN MUFA </t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>JHONATAN VICENTE ANASTACIO SAIRUTUPAC</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2026-09-08 01:42:37</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>2026-09-08 01:43:06</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>2026-09-08 01:43:08</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CM-20260905-00000305</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>235-ETH_LOS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0130176</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0130176_LM_Huanuco</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>CORTE</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>21:47:38</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>dispatched</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Edwin Oscco</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2026-09-05 18:45:35</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>'-</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>O&amp;M PEXT</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>dispatch</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>VICTOR WILLIAM CAUTI AGUIRRE</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
         <is>
           <t/>
         </is>
